--- a/data/supplementary_data.xlsx
+++ b/data/supplementary_data.xlsx
@@ -8873,7 +8873,7 @@
         <v>184.42</v>
       </c>
       <c r="R120" s="13">
-        <v>229.3</v>
+        <v>164.65</v>
       </c>
       <c r="S120" s="13">
         <v>209.26</v>
@@ -15743,7 +15743,7 @@
         <v>1</v>
       </c>
       <c r="P198" s="13">
-        <v>269.94</v>
+        <v>369.94</v>
       </c>
       <c r="Q198" s="13">
         <v>367.31</v>
